--- a/Internship/校外实习指导教师会议记录表.xlsx
+++ b/Internship/校外实习指导教师会议记录表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\Internship\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28E43DB-7C55-45A9-8A92-E113F8CD4DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48ED731F-F559-4E86-A4A6-C3DB5AB5DD00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B806E80-977E-4439-A627-1DEBBE366E55}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>班级</t>
   </si>
@@ -191,11 +191,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>签到表</t>
+    <t>校外实习指导教师会议记录表（一）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>校外实习指导教师会议记录表（一）</t>
+    <t>校外实习指导教师会议记录签到表（一）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4-302a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -203,7 +215,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -255,6 +267,13 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -342,28 +361,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -383,13 +380,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -417,23 +432,32 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -670,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D775EA53-2DD1-4C54-838E-E25C1853FA42}">
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.625" style="2" customWidth="1"/>
@@ -683,7 +707,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -734,16 +758,16 @@
       <c r="P3"/>
     </row>
     <row r="4" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
       <c r="I4"/>
       <c r="J4"/>
       <c r="K4"/>
@@ -754,14 +778,14 @@
       <c r="P4"/>
     </row>
     <row r="5" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="16"/>
-      <c r="B5" s="18" t="s">
+      <c r="A5" s="19"/>
+      <c r="B5" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
       <c r="I5"/>
       <c r="J5"/>
       <c r="K5"/>
@@ -772,14 +796,14 @@
       <c r="P5"/>
     </row>
     <row r="6" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="16"/>
-      <c r="B6" s="18" t="s">
+      <c r="A6" s="19"/>
+      <c r="B6" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
       <c r="I6"/>
       <c r="J6"/>
       <c r="K6"/>
@@ -790,14 +814,14 @@
       <c r="P6"/>
     </row>
     <row r="7" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="16"/>
-      <c r="B7" s="18" t="s">
+      <c r="A7" s="19"/>
+      <c r="B7" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
       <c r="I7"/>
       <c r="J7"/>
       <c r="K7"/>
@@ -808,14 +832,14 @@
       <c r="P7"/>
     </row>
     <row r="8" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="16"/>
-      <c r="B8" s="19" t="s">
+      <c r="A8" s="19"/>
+      <c r="B8" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -829,11 +853,11 @@
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -847,65 +871,81 @@
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="12"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="11"/>
+      <c r="A11" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="14"/>
     </row>
     <row r="12" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="7"/>
+      <c r="A12" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="17">
+        <v>46153</v>
+      </c>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="13" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F13" s="7"/>
     </row>
     <row r="14" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F14" s="7"/>
+      <c r="F15" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -919,11 +959,15 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12:B14 D12:D14 F12:F14" xr:uid="{3F5C90BC-5969-418B-8665-1ABF9C5E2885}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B13:B15 D13:D15 F13:F15" xr:uid="{3F5C90BC-5969-418B-8665-1ABF9C5E2885}">
       <formula1>"√,×"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L广州华立学院&amp;C计算机科学与技术&amp;R计算机工程学院</oddHeader>
+    <oddFooter>&amp;C广州·中国</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/Internship/校外实习指导教师会议记录表.xlsx
+++ b/Internship/校外实习指导教师会议记录表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\Internship\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\glplaman.github.io\internship\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48ED731F-F559-4E86-A4A6-C3DB5AB5DD00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C53383D-4AF6-402F-A9F2-F9CD6CABEF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B806E80-977E-4439-A627-1DEBBE366E55}"/>
   </bookViews>
@@ -69,9 +69,6 @@
     <t>黄钧笙</t>
   </si>
   <si>
-    <t>钟正杨</t>
-  </si>
-  <si>
     <t>肖航</t>
   </si>
   <si>
@@ -208,6 +205,10 @@
   </si>
   <si>
     <t>时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钟正扬</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -707,7 +708,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -720,7 +721,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>1</v>
@@ -762,7 +763,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" s="20"/>
       <c r="D4" s="20"/>
@@ -780,7 +781,7 @@
     <row r="5" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="19"/>
       <c r="B5" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="21"/>
       <c r="D5" s="21"/>
@@ -798,7 +799,7 @@
     <row r="6" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="19"/>
       <c r="B6" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" s="21"/>
       <c r="D6" s="21"/>
@@ -816,7 +817,7 @@
     <row r="7" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="19"/>
       <c r="B7" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="21"/>
       <c r="D7" s="21"/>
@@ -834,7 +835,7 @@
     <row r="8" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="19"/>
       <c r="B8" s="22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" s="22"/>
       <c r="D8" s="22"/>
@@ -881,7 +882,7 @@
     </row>
     <row r="11" spans="1:16" ht="48" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -891,7 +892,7 @@
     </row>
     <row r="12" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="17">
         <v>46153</v>
@@ -899,10 +900,10 @@
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
       <c r="E12" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.15">
@@ -911,11 +912,11 @@
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="4" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F13" s="7"/>
     </row>
@@ -925,11 +926,11 @@
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F14" s="7"/>
     </row>
@@ -939,11 +940,11 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F15" s="7"/>
     </row>
